--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B631934-04E1-4841-A7D0-23DF867CCE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C835BC3-7069-47AC-80BF-8299BEAD1422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>SAR</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-640</t>
   </si>
 </sst>
 </file>
@@ -460,7 +463,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -545,6 +548,41 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2">
+        <v>414</v>
+      </c>
+      <c r="E3" s="2">
+        <v>463</v>
+      </c>
+      <c r="F3" s="2">
+        <v>-49</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46</v>
+      </c>
+      <c r="H3" s="2">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
